--- a/jogos_2026-02-12.xlsx
+++ b/jogos_2026-02-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI33"/>
+  <dimension ref="A1:AI28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,76 +1016,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46065.5</v>
+        <v>46065.53125</v>
       </c>
     </row>
     <row r="6">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,76 +1135,76 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V6" t="n">
         <v>8.5</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46065.5</v>
+        <v>46065.58333333334</v>
       </c>
     </row>
     <row r="7">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,76 +1254,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46065.53125</v>
+        <v>46065.58333333334</v>
       </c>
     </row>
     <row r="8">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46065.58333333334</v>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1501,67 +1501,67 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46065.58333333334</v>
+        <v>46065.60416666666</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1620,67 +1620,67 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46065.58333333334</v>
+        <v>46065.60416666666</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46065.60416666666</v>
+        <v>46065.625</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46065.60416666666</v>
+        <v>46065.66666666666</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46065.625</v>
+        <v>46065.6875</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46065.625</v>
+        <v>46065.6875</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46065.66666666666</v>
+        <v>46065.6875</v>
       </c>
     </row>
     <row r="16">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46065.6875</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46065.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46065.6875</v>
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46065.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46065.6875</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,76 +2920,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46065.6875</v>
+        <v>46065.70833333334</v>
       </c>
     </row>
     <row r="22">
@@ -2998,27 +2998,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,76 +3039,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46065.6875</v>
+        <v>46065.79166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3117,27 +3117,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,76 +3158,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46065.6875</v>
+        <v>46065.8125</v>
       </c>
     </row>
     <row r="24">
@@ -3236,27 +3236,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,76 +3277,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.64</v>
+        <v>2.11</v>
       </c>
       <c r="M24" t="n">
-        <v>3.91</v>
+        <v>2.92</v>
       </c>
       <c r="N24" t="n">
-        <v>1.72</v>
+        <v>4.22</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46065.70833333334</v>
+        <v>46065.83333333334</v>
       </c>
     </row>
     <row r="25">
@@ -3355,27 +3355,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,17 +3392,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46065.79166666666</v>
+        <v>46065.875</v>
       </c>
     </row>
     <row r="26">
@@ -3474,27 +3474,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,17 +3511,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46065.8125</v>
+        <v>46065.875</v>
       </c>
     </row>
     <row r="27">
@@ -3593,27 +3593,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46065.83333333334</v>
+        <v>46065.875</v>
       </c>
     </row>
     <row r="28">
@@ -3712,27 +3712,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,670 +3753,75 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46065.875</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46065</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Morocco Botola Pro</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Olympic Safi</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>CR Khemis Zemamra</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="3" t="n">
-        <v>46065.875</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46065</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Morocco Botola Pro</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>FAR Rabat</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>RSB Berkane</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" s="3" t="n">
-        <v>46065.875</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>46065</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Morocco Botola Pro</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Maghreb Fès</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Wydad Casablanca</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" s="3" t="n">
-        <v>46065.875</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46065</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>El Bayadh</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>ASO Chlef</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="3" t="n">
-        <v>46065.875</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>46065</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M33" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" s="3" t="n">
         <v>46065.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-12.xlsx
+++ b/jogos_2026-02-12.xlsx
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.12</v>
+        <v>2.45</v>
       </c>
       <c r="O19" t="n">
-        <v>2.79</v>
+        <v>3.44</v>
       </c>
       <c r="P19" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.98</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46065.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.62</v>
+        <v>2.14</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="O20" t="n">
-        <v>3.44</v>
+        <v>2.79</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>3.98</v>
       </c>
       <c r="R20" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="W20" t="n">
         <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46065.6875</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
         <v>2.8</v>
@@ -3057,7 +3057,7 @@
         <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
         <v>2.36</v>
@@ -3066,7 +3066,7 @@
         <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
         <v>7</v>
@@ -3081,7 +3081,7 @@
         <v>1.34</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA22" t="n">
         <v>2.15</v>
@@ -3090,16 +3090,16 @@
         <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="AD22" t="n">
         <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AG22" t="n">
         <v>1.38</v>
@@ -3164,7 +3164,7 @@
         <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
         <v>2.79</v>
@@ -3176,16 +3176,16 @@
         <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S23" t="n">
-        <v>2.85</v>
+        <v>2.44</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
         <v>7</v>
@@ -3203,28 +3203,28 @@
         <v>3.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AC23" t="n">
         <v>3.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
         <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46065.8125</v>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="M24" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>4.22</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
         <v>2.54</v>
@@ -3295,19 +3295,19 @@
         <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="U24" t="n">
         <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.02</v>
@@ -3319,13 +3319,13 @@
         <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC24" t="n">
         <v>3.62</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.09</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="O28" t="n">
         <v>3.45</v>
@@ -3768,7 +3768,7 @@
         <v>2.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="R28" t="n">
         <v>1.43</v>
@@ -3780,7 +3780,7 @@
         <v>2.81</v>
       </c>
       <c r="U28" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V28" t="n">
         <v>7.1</v>
@@ -3792,7 +3792,7 @@
         <v>1.06</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z28" t="n">
         <v>3.3</v>
@@ -3801,22 +3801,22 @@
         <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
         <v>3.12</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AF28" t="n">
         <v>1.95</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AH28" t="n">
         <v>1.32</v>

--- a/jogos_2026-02-12.xlsx
+++ b/jogos_2026-02-12.xlsx
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>3.63</v>
+        <v>3.69</v>
       </c>
       <c r="O12" t="n">
         <v>2.33</v>
       </c>
       <c r="P12" t="n">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>4.17</v>
       </c>
       <c r="R12" t="n">
         <v>1.23</v>
@@ -1891,13 +1891,13 @@
         <v>1.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
         <v>1.53</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
         <v>2.31</v>
@@ -1906,16 +1906,16 @@
         <v>1.57</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AG12" t="n">
         <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46065.66666666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.5</v>
       </c>
-      <c r="M14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.41</v>
-      </c>
       <c r="T14" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.98</v>
+        <v>3.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46065.6875</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.54</v>
+        <v>2.15</v>
       </c>
       <c r="M15" t="n">
-        <v>3.38</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>1.71</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>7.02</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.14</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="T15" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="V15" t="n">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.03</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.42</v>
+        <v>4.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46065.6875</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>4.54</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>1.71</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>7.02</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.8</v>
+        <v>2.14</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="W16" t="n">
         <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
         <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.01</v>
+        <v>1.06</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46065.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U18" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
         <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.55</v>
+        <v>2.01</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46065.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.62</v>
+        <v>2.14</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="O19" t="n">
-        <v>3.44</v>
+        <v>2.79</v>
       </c>
       <c r="P19" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>3.98</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46065.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>3.12</v>
+        <v>2.62</v>
       </c>
       <c r="O20" t="n">
-        <v>2.79</v>
+        <v>3.18</v>
       </c>
       <c r="P20" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="Q20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC20" t="n">
         <v>3.98</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46065.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G27" t="n">

--- a/jogos_2026-02-12.xlsx
+++ b/jogos_2026-02-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI28"/>
+  <dimension ref="A1:AI30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,90 +642,90 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46065.375</v>
@@ -761,90 +761,90 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46065.41666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,19 +990,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1012,80 +1012,80 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="N5" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>4.78</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.48</v>
+        <v>2.82</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>2.53</v>
+        <v>2.27</v>
       </c>
       <c r="T5" t="n">
-        <v>3.02</v>
+        <v>3.34</v>
       </c>
       <c r="U5" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>8</v>
+        <v>9.1</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.81</v>
+        <v>2.49</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>1.31</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46065.53125</v>
+        <v>46065.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,102 +1109,102 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O6" t="n">
-        <v>2.78</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.01</v>
+        <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.4</v>
+        <v>2.38</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V6" t="n">
+        <v>7</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z6" t="n">
         <v>3.08</v>
       </c>
-      <c r="U6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
         <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46065.58333333334</v>
+        <v>46065.53125</v>
       </c>
     </row>
     <row r="7">
@@ -1237,90 +1237,90 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
         <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.67</v>
+        <v>2.79</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.34</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="S7" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="T7" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="V7" t="n">
-        <v>8.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC7" t="n">
         <v>3.45</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46065.58333333334</v>
@@ -1347,99 +1347,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>4.13</v>
       </c>
       <c r="O8" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>4.83</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="T8" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="V8" t="n">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.03</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46065.58333333334</v>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,102 +1466,102 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.39</v>
+        <v>4.51</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="U9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.34</v>
       </c>
-      <c r="V9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.3</v>
-      </c>
       <c r="Z9" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46065.60416666666</v>
+        <v>46065.58333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1585,99 +1585,99 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
-        <v>2.01</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="U10" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="V10" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.43</v>
+        <v>3.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46065.60416666666</v>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,16 +1704,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1726,80 +1726,80 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="P11" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.44</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V11" t="n">
-        <v>9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46065.625</v>
+        <v>46065.60416666666</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,102 +1823,102 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>3.69</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.33</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.17</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>3.36</v>
+        <v>2.24</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.59</v>
+        <v>1.21</v>
       </c>
       <c r="V12" t="n">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.12</v>
+        <v>1.41</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.8</v>
+        <v>2.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.53</v>
+        <v>2.69</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.31</v>
+        <v>5.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>2.24</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.88</v>
+        <v>1.28</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46065.66666666666</v>
+        <v>46065.625</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,19 +1942,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1964,80 +1964,80 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>3.68</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="P13" t="n">
-        <v>2.21</v>
+        <v>2.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="U13" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.05</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.15</v>
+        <v>2.52</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46065.6875</v>
+        <v>46065.66666666666</v>
       </c>
     </row>
     <row r="14">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,99 +2061,99 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="N14" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.97</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>7.4</v>
+        <v>5.35</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG14" t="n">
+      <c r="AH14" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.42</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46065.6875</v>
@@ -2180,16 +2180,16 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -2202,77 +2202,77 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>3.07</v>
       </c>
       <c r="P15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S15" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46065.6875</v>
@@ -2311,87 +2311,87 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="N16" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="O16" t="n">
-        <v>7.02</v>
+        <v>4.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T16" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
         <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.68</v>
       </c>
-      <c r="AC16" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46065.6875</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,16 +2418,16 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.13</v>
+        <v>2.75</v>
       </c>
       <c r="N17" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.43</v>
+        <v>4.46</v>
       </c>
       <c r="R17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.35</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.74</v>
+        <v>1.47</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46065.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,99 +2537,99 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="M18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.5</v>
       </c>
-      <c r="N18" t="n">
-        <v>5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T18" t="n">
-        <v>3.04</v>
+        <v>2.05</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="V18" t="n">
-        <v>7.6</v>
+        <v>4.55</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC18" t="n">
         <v>2.13</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.21</v>
+        <v>1.74</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.03</v>
+        <v>1.47</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.67</v>
+        <v>2.58</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46065.6875</v>
@@ -2656,99 +2656,99 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.14</v>
+        <v>3.25</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="N19" t="n">
-        <v>3.12</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>2.79</v>
+        <v>4.35</v>
       </c>
       <c r="P19" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.98</v>
+        <v>2.98</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="S19" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.97</v>
+        <v>2.46</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.02</v>
+        <v>2.41</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46065.6875</v>
@@ -2775,99 +2775,99 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S20" t="n">
         <v>2.5</v>
       </c>
-      <c r="M20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.41</v>
-      </c>
       <c r="T20" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="U20" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.43</v>
+        <v>2.3</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46065.6875</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,102 +2894,102 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.88</v>
+        <v>1.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.97</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>1.71</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>4.72</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>3.15</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.73</v>
+        <v>2.88</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.04</v>
+        <v>3.58</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.18</v>
+        <v>1.77</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46065.70833333334</v>
+        <v>46065.6875</v>
       </c>
     </row>
     <row r="22">
@@ -2998,117 +2998,117 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>3.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="O22" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.8</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AB22" t="n">
         <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.65</v>
+        <v>1.09</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46065.79166666666</v>
+        <v>46065.70833333334</v>
       </c>
     </row>
     <row r="23">
@@ -3117,34 +3117,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -3154,80 +3154,80 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.86</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>1.67</v>
       </c>
       <c r="O23" t="n">
-        <v>2.79</v>
+        <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.04</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.5</v>
+        <v>2.86</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46065.8125</v>
+        <v>46065.70833333334</v>
       </c>
     </row>
     <row r="24">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,76 +3277,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="P24" t="n">
         <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
         <v>1.45</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>3.27</v>
+        <v>2.94</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
         <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.62</v>
+        <v>3.86</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46065.83333333334</v>
+        <v>46065.79166666666</v>
       </c>
     </row>
     <row r="25">
@@ -3355,27 +3355,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,80 +3392,80 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46065.875</v>
+        <v>46065.8125</v>
       </c>
     </row>
     <row r="26">
@@ -3474,27 +3474,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,80 +3511,80 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46065.875</v>
+        <v>46065.83333333334</v>
       </c>
     </row>
     <row r="27">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3712,116 +3712,354 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Maghreb Fès</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Wydad Casablanca</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3" t="n">
+        <v>46065.875</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FAR Rabat</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>RSB Berkane</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3" t="n">
+        <v>46065.875</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Palmeiras</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="L30" t="n">
+        <v>3</v>
+      </c>
+      <c r="M30" t="n">
         <v>3.2</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="O28" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y28" t="n">
+      <c r="N30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="Z30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA30" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC28" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD28" t="n">
+      <c r="AB30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE28" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG28" t="n">
+      <c r="AE30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.35</v>
       </c>
-      <c r="AH28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI28" s="3" t="n">
+      <c r="AI30" s="3" t="n">
         <v>46065.89583333334</v>
       </c>
     </row>
